--- a/tests/fixtures/calderwood/calderwood_management_accounts.xlsx
+++ b/tests/fixtures/calderwood/calderwood_management_accounts.xlsx
@@ -468,10 +468,22 @@
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>Year end (EoP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Continuing operations</t>
         </is>
